--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_los_rios.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_los_rios.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.69134659022497</v>
+      </c>
+      <c r="C2">
         <v>31.26360344172864</v>
-      </c>
-      <c r="C2">
-        <v>24.69134659022497</v>
       </c>
       <c r="D2">
         <v>3.198607613686861</v>
       </c>
       <c r="E2">
-        <v>20.04656051976744</v>
+        <v>15.83235837347001</v>
       </c>
       <c r="F2">
         <v>64.12108110676256</v>
       </c>
       <c r="G2">
-        <v>15.83235837347001</v>
+        <v>20.04656051976744</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.27260458839406</v>
+      </c>
+      <c r="C3">
         <v>41.63292847503374</v>
-      </c>
-      <c r="C3">
-        <v>28.27260458839406</v>
       </c>
       <c r="D3">
         <v>2.40194489465154</v>
       </c>
       <c r="E3">
-        <v>24.50357426528991</v>
+        <v>16.64019062748213</v>
       </c>
       <c r="F3">
         <v>58.85623510722795</v>
       </c>
       <c r="G3">
-        <v>16.64019062748213</v>
+        <v>24.50357426528991</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>28.88767918708038</v>
+      </c>
+      <c r="C4">
         <v>35.80112502268191</v>
-      </c>
-      <c r="C4">
-        <v>28.88767918708038</v>
       </c>
       <c r="D4">
         <v>2.793208312214901</v>
       </c>
       <c r="E4">
-        <v>21.73865138827678</v>
+        <v>17.54076685764654</v>
       </c>
       <c r="F4">
         <v>60.72058175407669</v>
       </c>
       <c r="G4">
-        <v>17.54076685764654</v>
+        <v>21.73865138827678</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.23853923853924</v>
+      </c>
+      <c r="C5">
         <v>35.17482517482517</v>
-      </c>
-      <c r="C5">
-        <v>29.23853923853924</v>
       </c>
       <c r="D5">
         <v>2.842942345924453</v>
       </c>
       <c r="E5">
-        <v>21.39413988657845</v>
+        <v>17.78355387523629</v>
       </c>
       <c r="F5">
         <v>60.82230623818526</v>
       </c>
       <c r="G5">
-        <v>17.78355387523629</v>
+        <v>21.39413988657845</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.07319698600646</v>
+      </c>
+      <c r="C6">
         <v>37.00753498385361</v>
-      </c>
-      <c r="C6">
-        <v>28.07319698600646</v>
       </c>
       <c r="D6">
         <v>2.702152414194299</v>
       </c>
       <c r="E6">
-        <v>22.41784037558686</v>
+        <v>17.0057381324987</v>
       </c>
       <c r="F6">
         <v>60.57642149191445</v>
       </c>
       <c r="G6">
-        <v>17.0057381324987</v>
+        <v>22.41784037558686</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>31.51305085944684</v>
+      </c>
+      <c r="C7">
         <v>31.44231449388131</v>
-      </c>
-      <c r="C7">
-        <v>31.51305085944684</v>
       </c>
       <c r="D7">
         <v>3.180427446569179</v>
       </c>
       <c r="E7">
-        <v>19.29504709814646</v>
+        <v>19.33845552806355</v>
       </c>
       <c r="F7">
         <v>61.36649737378999</v>
       </c>
       <c r="G7">
-        <v>19.33845552806355</v>
+        <v>19.29504709814646</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.98562236873461</v>
+      </c>
+      <c r="C8">
         <v>37.81078719517038</v>
-      </c>
-      <c r="C8">
-        <v>28.98562236873461</v>
       </c>
       <c r="D8">
         <v>2.644747899159664</v>
       </c>
       <c r="E8">
+        <v>17.37784550909611</v>
+      </c>
+      <c r="F8">
+        <v>59.95332888846558</v>
+      </c>
+      <c r="G8">
         <v>22.66882560243833</v>
-      </c>
-      <c r="F8">
-        <v>59.95332888846556</v>
-      </c>
-      <c r="G8">
-        <v>17.3778455090961</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.71147260273973</v>
+      </c>
+      <c r="C9">
         <v>33.48458904109589</v>
-      </c>
-      <c r="C9">
-        <v>28.71147260273973</v>
       </c>
       <c r="D9">
         <v>2.986448478649962</v>
       </c>
       <c r="E9">
-        <v>20.64451423896118</v>
+        <v>17.70170761962575</v>
       </c>
       <c r="F9">
         <v>61.65377814141308</v>
       </c>
       <c r="G9">
-        <v>17.70170761962575</v>
+        <v>20.64451423896118</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.4793442355532</v>
+      </c>
+      <c r="C10">
         <v>37.39651727091064</v>
-      </c>
-      <c r="C10">
-        <v>26.4793442355532</v>
       </c>
       <c r="D10">
         <v>2.674045801526717</v>
       </c>
       <c r="E10">
+        <v>16.15817240692813</v>
+      </c>
+      <c r="F10">
+        <v>61.0217997212821</v>
+      </c>
+      <c r="G10">
         <v>22.82002787178977</v>
-      </c>
-      <c r="F10">
-        <v>61.02179972128211</v>
-      </c>
-      <c r="G10">
-        <v>16.15817240692813</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>31.06619504800404</v>
+      </c>
+      <c r="C11">
         <v>32.67306720565942</v>
-      </c>
-      <c r="C11">
-        <v>31.06619504800404</v>
       </c>
       <c r="D11">
         <v>3.060624806681101</v>
       </c>
       <c r="E11">
-        <v>19.95432662634243</v>
+        <v>18.97296630045673</v>
       </c>
       <c r="F11">
         <v>61.07270707320084</v>
       </c>
       <c r="G11">
-        <v>18.97296630045673</v>
+        <v>19.95432662634243</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.54509141189123</v>
+      </c>
+      <c r="C12">
         <v>38.19327085573821</v>
-      </c>
-      <c r="C12">
-        <v>28.54509141189123</v>
       </c>
       <c r="D12">
         <v>2.618262268704747</v>
       </c>
       <c r="E12">
-        <v>22.90610890997881</v>
+        <v>17.11969040818207</v>
       </c>
       <c r="F12">
         <v>59.97420068183912</v>
       </c>
       <c r="G12">
-        <v>17.11969040818207</v>
+        <v>22.90610890997881</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>33.2117204423669</v>
+      </c>
+      <c r="C13">
         <v>20.23714513738456</v>
-      </c>
-      <c r="C13">
-        <v>33.2117204423669</v>
       </c>
       <c r="D13">
         <v>4.941408450704225</v>
       </c>
       <c r="E13">
+        <v>21.6435099190133</v>
+      </c>
+      <c r="F13">
+        <v>65.16828887733115</v>
+      </c>
+      <c r="G13">
         <v>13.18820120365555</v>
-      </c>
-      <c r="F13">
-        <v>65.16828887733116</v>
-      </c>
-      <c r="G13">
-        <v>21.6435099190133</v>
       </c>
     </row>
   </sheetData>
